--- a/roles.xlsx
+++ b/roles.xlsx
@@ -469,9 +469,10 @@
           <t>central</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>central, lateral_left, lateral_right, corner_left, corner_right, pouf_lateral, pouf_frontal, table_lateral, table_frontal, chaise_longue</t>
+          <t>central, lateral_left, lateral_right, corner_left, corner_right, pouf_lateral, pouf_frontal, table_lateral, table_frontal, chaise_longue, chaise_longue_left, chaise_longue_right</t>
         </is>
       </c>
     </row>
@@ -496,9 +497,10 @@
           <t>lateral_left</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>central, lateral_left, lateral_right, corner_left, corner_right, pouf_lateral, pouf_frontal, table_lateral, table_frontal, chaise_longue</t>
+          <t>central, lateral_left, lateral_right, corner_left, corner_right, pouf_lateral, pouf_frontal, table_lateral, table_frontal, chaise_longue, chaise_longue_left, chaise_longue_right</t>
         </is>
       </c>
     </row>
@@ -523,9 +525,10 @@
           <t>lateral_right</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>central, lateral_left, lateral_right, corner_left, corner_right, pouf_lateral, pouf_frontal, table_lateral, table_frontal, chaise_longue</t>
+          <t>central, lateral_left, lateral_right, corner_left, corner_right, pouf_lateral, pouf_frontal, table_lateral, table_frontal, chaise_longue, chaise_longue_left, chaise_longue_right</t>
         </is>
       </c>
     </row>
@@ -550,9 +553,10 @@
           <t>corner_left</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>central, lateral_left, lateral_right, corner_left, corner_right, pouf_lateral, pouf_frontal, table_lateral, table_frontal, chaise_longue</t>
+          <t>central, lateral_left, lateral_right, corner_left, corner_right, pouf_lateral, pouf_frontal, table_lateral, table_frontal, chaise_longue, chaise_longue_left, chaise_longue_right</t>
         </is>
       </c>
     </row>
@@ -577,9 +581,10 @@
           <t>corner_right</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>central, lateral_left, lateral_right, corner_left, corner_right, pouf_lateral, pouf_frontal, table_lateral, table_frontal, chaise_longue</t>
+          <t>central, lateral_left, lateral_right, corner_left, corner_right, pouf_lateral, pouf_frontal, table_lateral, table_frontal, chaise_longue, chaise_longue_left, chaise_longue_right</t>
         </is>
       </c>
     </row>
@@ -591,22 +596,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pouf-209721_bm3</t>
+          <t>Pouf_frontal-209721_bm3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>261+Poufs</t>
+          <t>381+Outdoor sofas</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>pouf_lateral</t>
-        </is>
-      </c>
+          <t>pouf_frontal</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>central, lateral_left, lateral_right, corner_left, corner_right, pouf_lateral, pouf_frontal, table_lateral, table_frontal, chaise_longue</t>
+          <t>central, lateral_left, lateral_right, corner_left, corner_right, pouf_lateral, pouf_frontal, table_lateral, table_frontal, chaise_longue, chaise_longue_left, chaise_longue_right</t>
         </is>
       </c>
     </row>
@@ -618,22 +624,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pouf-209721_bm3</t>
+          <t>Pouf_lateral-209721_bm3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>261+Poufs</t>
+          <t>381+Outdoor sofas</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>pouf_frontal</t>
-        </is>
-      </c>
+          <t>pouf_lateral</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>central, lateral_left, lateral_right, corner_left, corner_right, pouf_lateral, pouf_frontal, table_lateral, table_frontal, chaise_longue</t>
+          <t>central, lateral_left, lateral_right, corner_left, corner_right, pouf_lateral, pouf_frontal, table_lateral, table_frontal, chaise_longue, chaise_longue_left, chaise_longue_right</t>
         </is>
       </c>
     </row>
@@ -650,17 +657,18 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>92+Coffee tables</t>
+          <t>381+Outdoor sofas</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>table_lateral</t>
-        </is>
-      </c>
+          <t>table_frontal</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>central, lateral_left, lateral_right, corner_left, corner_right, pouf_lateral, pouf_frontal, table_lateral, table_frontal, chaise_longue</t>
+          <t>central, lateral_left, lateral_right, corner_left, corner_right, pouf_lateral, pouf_frontal, table_lateral, table_frontal, chaise_longue, chaise_longue_left, chaise_longue_right</t>
         </is>
       </c>
     </row>
@@ -677,17 +685,18 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>92+Coffee tables</t>
+          <t>381+Outdoor sofas</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>table_frontal</t>
-        </is>
-      </c>
+          <t>table_lateral</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>central, lateral_left, lateral_right, corner_left, corner_right, pouf_lateral, pouf_frontal, table_lateral, table_frontal, chaise_longue</t>
+          <t>central, lateral_left, lateral_right, corner_left, corner_right, pouf_lateral, pouf_frontal, table_lateral, table_frontal, chaise_longue, chaise_longue_left, chaise_longue_right</t>
         </is>
       </c>
     </row>
